--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-EX-SupplyOptionsType.xlsx
@@ -1743,7 +1743,7 @@
         <v>87</v>
       </c>
       <c r="AI9" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ9" t="s" s="2">
         <v>123</v>
@@ -2262,7 +2262,7 @@
         <v>87</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ14" t="s" s="2">
         <v>123</v>
@@ -2781,7 +2781,7 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>123</v>
@@ -2989,7 +2989,7 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>123</v>
